--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="7" activeTab="8"/>
+    <workbookView windowWidth="28800" windowHeight="14175" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,9 @@
     <sheet name="AI配置" sheetId="16" r:id="rId16"/>
     <sheet name="战斗公式" sheetId="17" r:id="rId17"/>
     <sheet name="地图生成参数" sheetId="18" r:id="rId18"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId19"/>
+    <sheet name="核心玩法配置" sheetId="19" r:id="rId19"/>
+    <sheet name="表现配置" sheetId="20" r:id="rId20"/>
+    <sheet name="山体配置" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="490">
   <si>
     <t>unitId</t>
   </si>
@@ -1169,6 +1171,357 @@
   </si>
   <si>
     <t>map_gen.main</t>
+  </si>
+  <si>
+    <t>movementSpeedPerPoint</t>
+  </si>
+  <si>
+    <t>attackDashSpeed</t>
+  </si>
+  <si>
+    <t>unitRotationSpeed</t>
+  </si>
+  <si>
+    <t>attackArrivalThreshold</t>
+  </si>
+  <si>
+    <t>attackReturnThreshold</t>
+  </si>
+  <si>
+    <t>attackAnimationDuration</t>
+  </si>
+  <si>
+    <t>unitDeathDestroyDelay</t>
+  </si>
+  <si>
+    <t>buildingHealIntervalFallback</t>
+  </si>
+  <si>
+    <t>unitPathSearchThrottle</t>
+  </si>
+  <si>
+    <t>barracksSpawnInterval</t>
+  </si>
+  <si>
+    <t>barracksFallbackUnitLegacyId</t>
+  </si>
+  <si>
+    <t>arrowTowerRange</t>
+  </si>
+  <si>
+    <t>arrowTowerAttackInterval</t>
+  </si>
+  <si>
+    <t>arrowTowerDamage</t>
+  </si>
+  <si>
+    <t>arrowTowerArcHeight</t>
+  </si>
+  <si>
+    <t>arrowTowerFlightDuration</t>
+  </si>
+  <si>
+    <t>centralChestHp</t>
+  </si>
+  <si>
+    <t>handCardLimit</t>
+  </si>
+  <si>
+    <t>initialHandCardCount</t>
+  </si>
+  <si>
+    <t>tacticalCardSlotCount</t>
+  </si>
+  <si>
+    <t>talentOfferCount</t>
+  </si>
+  <si>
+    <t>publicBuildingMaxCount</t>
+  </si>
+  <si>
+    <t>publicBuildingMinLandNeighbors</t>
+  </si>
+  <si>
+    <t>publicBuildingArenaReserveExtraRings</t>
+  </si>
+  <si>
+    <t>每点移动力换算的世界移动速度</t>
+  </si>
+  <si>
+    <t>近战攻击冲刺与返回速度</t>
+  </si>
+  <si>
+    <t>单位移动和攻击转向速度</t>
+  </si>
+  <si>
+    <t>攻击冲刺到达目标的距离阈值</t>
+  </si>
+  <si>
+    <t>攻击后返回原位的距离阈值</t>
+  </si>
+  <si>
+    <t>攻击动画持续时间（秒）</t>
+  </si>
+  <si>
+    <t>单位死亡后销毁延迟（秒）</t>
+  </si>
+  <si>
+    <t>祭坛回血间隔缺失时的兜底秒数</t>
+  </si>
+  <si>
+    <t>单位寻路失败后的重试节流次数</t>
+  </si>
+  <si>
+    <t>兵营生产单位间隔（秒）</t>
+  </si>
+  <si>
+    <t>兵营未配置 producedUnit 时的旧单位ID兜底</t>
+  </si>
+  <si>
+    <t>箭塔基础攻击范围（格）</t>
+  </si>
+  <si>
+    <t>箭塔攻击间隔（秒）</t>
+  </si>
+  <si>
+    <t>箭塔每次射击伤害</t>
+  </si>
+  <si>
+    <t>箭矢弹道抛物线高度</t>
+  </si>
+  <si>
+    <t>箭矢飞行与伤害结算延迟（秒）</t>
+  </si>
+  <si>
+    <t>竞技场中央宝箱生命值</t>
+  </si>
+  <si>
+    <t>玩家与AI共享的手牌上限</t>
+  </si>
+  <si>
+    <t>玩家与AI开局初始手牌数量</t>
+  </si>
+  <si>
+    <t>战术卡可用槽位数量</t>
+  </si>
+  <si>
+    <t>每次天赋选择展示的候选卡数量</t>
+  </si>
+  <si>
+    <t>每局公共建筑生成数量上限</t>
+  </si>
+  <si>
+    <t>公共建筑候选根格最少陆地邻居数</t>
+  </si>
+  <si>
+    <t>公共建筑避开竞技场预留区的额外环数</t>
+  </si>
+  <si>
+    <t>gameplay.main</t>
+  </si>
+  <si>
+    <t>fogRefreshInterval</t>
+  </si>
+  <si>
+    <t>cameraShakeFrequency</t>
+  </si>
+  <si>
+    <t>unaffordableCardDim</t>
+  </si>
+  <si>
+    <t>talentScreenShakeStrength</t>
+  </si>
+  <si>
+    <t>talentScreenShakeDuration</t>
+  </si>
+  <si>
+    <t>迷雾纹理刷新间隔（秒）</t>
+  </si>
+  <si>
+    <t>相机震动频率（Hz）</t>
+  </si>
+  <si>
+    <t>卡牌不可购买时的暗淡系数（0~1）</t>
+  </si>
+  <si>
+    <t>天赋卡选择震屏强度</t>
+  </si>
+  <si>
+    <t>天赋卡选择震屏时长（秒）</t>
+  </si>
+  <si>
+    <t>feel.main</t>
+  </si>
+  <si>
+    <t>ridgeCount</t>
+  </si>
+  <si>
+    <t>minRidgeLength</t>
+  </si>
+  <si>
+    <t>maxRidgeLength</t>
+  </si>
+  <si>
+    <t>widthRadius</t>
+  </si>
+  <si>
+    <t>ridgeMinSpacing</t>
+  </si>
+  <si>
+    <t>scoreHeightWeight</t>
+  </si>
+  <si>
+    <t>scoreDropWeight</t>
+  </si>
+  <si>
+    <t>scoreTurnPenalty</t>
+  </si>
+  <si>
+    <t>flatHeightThreshold</t>
+  </si>
+  <si>
+    <t>baseHeight</t>
+  </si>
+  <si>
+    <t>minHeight</t>
+  </si>
+  <si>
+    <t>maxHeight</t>
+  </si>
+  <si>
+    <t>heightPerLength</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>ridgeNoiseAmplitude</t>
+  </si>
+  <si>
+    <t>cellNoiseScale</t>
+  </si>
+  <si>
+    <t>minVisibleHeight</t>
+  </si>
+  <si>
+    <t>maxSlopeRatio</t>
+  </si>
+  <si>
+    <t>xzPerturbRatio</t>
+  </si>
+  <si>
+    <t>peakEccentricMinRatio</t>
+  </si>
+  <si>
+    <t>peakEccentricMaxRatio</t>
+  </si>
+  <si>
+    <t>debugSingleCellAndStraightRidge</t>
+  </si>
+  <si>
+    <t>debugStraightRidgeLength</t>
+  </si>
+  <si>
+    <t>triplanarWorldScale</t>
+  </si>
+  <si>
+    <t>triplanarBlendSharpness</t>
+  </si>
+  <si>
+    <t>roughness</t>
+  </si>
+  <si>
+    <t>metallic</t>
+  </si>
+  <si>
+    <t>shadowStrength</t>
+  </si>
+  <si>
+    <t>期望山脉数量（0=不生成）</t>
+  </si>
+  <si>
+    <t>脊线最短长度（格）</t>
+  </si>
+  <si>
+    <t>脊线最长长度（格）</t>
+  </si>
+  <si>
+    <t>宽度化半径（格距）</t>
+  </si>
+  <si>
+    <t>新脊线起点与已有山格最小距离</t>
+  </si>
+  <si>
+    <t>走向评分：高度权重</t>
+  </si>
+  <si>
+    <t>走向评分：落差权重</t>
+  </si>
+  <si>
+    <t>走向评分：转向惩罚权重</t>
+  </si>
+  <si>
+    <t>平坦区高度差阈值</t>
+  </si>
+  <si>
+    <t>脊线基准高度（世界单位）</t>
+  </si>
+  <si>
+    <t>脊线高度下限（世界单位）</t>
+  </si>
+  <si>
+    <t>脊线高度上限（世界单位）</t>
+  </si>
+  <si>
+    <t>高度随脊线长度增量（每格）</t>
+  </si>
+  <si>
+    <t>垂直脊线衰减指数</t>
+  </si>
+  <si>
+    <t>沿脊线起伏幅度</t>
+  </si>
+  <si>
+    <t>每格噪声幅度</t>
+  </si>
+  <si>
+    <t>最小可见隆起（世界单位）</t>
+  </si>
+  <si>
+    <t>最大坡度比</t>
+  </si>
+  <si>
+    <t>控制点 XZ 扰动比</t>
+  </si>
+  <si>
+    <t>主峰偏心量下限比</t>
+  </si>
+  <si>
+    <t>主峰偏心量上限比</t>
+  </si>
+  <si>
+    <t>调试：绕过正常生成</t>
+  </si>
+  <si>
+    <t>调试直脊线长度（格）</t>
+  </si>
+  <si>
+    <t>Triplanar 世界缩放</t>
+  </si>
+  <si>
+    <t>Triplanar 权重锐度</t>
+  </si>
+  <si>
+    <t>表面粗糙度</t>
+  </si>
+  <si>
+    <t>金属度</t>
+  </si>
+  <si>
+    <t>阴影强度</t>
+  </si>
+  <si>
+    <t>mountain.main</t>
   </si>
 </sst>
 </file>
@@ -3725,14 +4078,6 @@
   <sheetPr/>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
-  <cols>
-    <col min="2" max="2" width="18.125" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="4" width="25.25" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
-    <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
@@ -3904,12 +4249,6 @@
   <sheetPr/>
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
-  <cols>
-    <col min="2" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="4" width="19.125" customWidth="1"/>
-    <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -3980,9 +4319,241 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:Y3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="A1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J1" t="s">
+        <v>381</v>
+      </c>
+      <c r="K1" t="s">
+        <v>382</v>
+      </c>
+      <c r="L1" t="s">
+        <v>383</v>
+      </c>
+      <c r="M1" t="s">
+        <v>384</v>
+      </c>
+      <c r="N1" t="s">
+        <v>385</v>
+      </c>
+      <c r="O1" t="s">
+        <v>386</v>
+      </c>
+      <c r="P1" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S1" t="s">
+        <v>390</v>
+      </c>
+      <c r="T1" t="s">
+        <v>391</v>
+      </c>
+      <c r="U1" t="s">
+        <v>392</v>
+      </c>
+      <c r="V1" t="s">
+        <v>393</v>
+      </c>
+      <c r="W1" t="s">
+        <v>394</v>
+      </c>
+      <c r="X1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L2" t="s">
+        <v>407</v>
+      </c>
+      <c r="M2" t="s">
+        <v>408</v>
+      </c>
+      <c r="N2" t="s">
+        <v>409</v>
+      </c>
+      <c r="O2" t="s">
+        <v>410</v>
+      </c>
+      <c r="P2" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>412</v>
+      </c>
+      <c r="R2" t="s">
+        <v>413</v>
+      </c>
+      <c r="S2" t="s">
+        <v>414</v>
+      </c>
+      <c r="T2" t="s">
+        <v>415</v>
+      </c>
+      <c r="U2" t="s">
+        <v>416</v>
+      </c>
+      <c r="V2" t="s">
+        <v>417</v>
+      </c>
+      <c r="W2" t="s">
+        <v>418</v>
+      </c>
+      <c r="X2" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>1.5</v>
+      </c>
+      <c r="F3">
+        <v>0.2</v>
+      </c>
+      <c r="G3">
+        <v>1.5</v>
+      </c>
+      <c r="H3">
+        <v>2.2</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>15</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>15</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>0.3</v>
+      </c>
+      <c r="R3">
+        <v>500</v>
+      </c>
+      <c r="S3">
+        <v>5</v>
+      </c>
+      <c r="T3">
+        <v>5</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -4235,6 +4806,357 @@
       </c>
       <c r="I9">
         <v>1.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3">
+        <v>0.05</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>0.45</v>
+      </c>
+      <c r="E3">
+        <v>0.15</v>
+      </c>
+      <c r="F3">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AC3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E1" t="s">
+        <v>436</v>
+      </c>
+      <c r="F1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G1" t="s">
+        <v>438</v>
+      </c>
+      <c r="H1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J1" t="s">
+        <v>441</v>
+      </c>
+      <c r="K1" t="s">
+        <v>442</v>
+      </c>
+      <c r="L1" t="s">
+        <v>443</v>
+      </c>
+      <c r="M1" t="s">
+        <v>444</v>
+      </c>
+      <c r="N1" t="s">
+        <v>445</v>
+      </c>
+      <c r="O1" t="s">
+        <v>446</v>
+      </c>
+      <c r="P1" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R1" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1" t="s">
+        <v>450</v>
+      </c>
+      <c r="T1" t="s">
+        <v>451</v>
+      </c>
+      <c r="U1" t="s">
+        <v>452</v>
+      </c>
+      <c r="V1" t="s">
+        <v>453</v>
+      </c>
+      <c r="W1" t="s">
+        <v>454</v>
+      </c>
+      <c r="X1" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>456</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>457</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>458</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>459</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F2" t="s">
+        <v>465</v>
+      </c>
+      <c r="G2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I2" t="s">
+        <v>468</v>
+      </c>
+      <c r="J2" t="s">
+        <v>469</v>
+      </c>
+      <c r="K2" t="s">
+        <v>470</v>
+      </c>
+      <c r="L2" t="s">
+        <v>471</v>
+      </c>
+      <c r="M2" t="s">
+        <v>472</v>
+      </c>
+      <c r="N2" t="s">
+        <v>473</v>
+      </c>
+      <c r="O2" t="s">
+        <v>474</v>
+      </c>
+      <c r="P2" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R2" t="s">
+        <v>477</v>
+      </c>
+      <c r="S2" t="s">
+        <v>478</v>
+      </c>
+      <c r="T2" t="s">
+        <v>479</v>
+      </c>
+      <c r="U2" t="s">
+        <v>480</v>
+      </c>
+      <c r="V2" t="s">
+        <v>481</v>
+      </c>
+      <c r="W2" t="s">
+        <v>482</v>
+      </c>
+      <c r="X2" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>485</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>486</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>487</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1.2</v>
+      </c>
+      <c r="L3">
+        <v>0.8</v>
+      </c>
+      <c r="M3">
+        <v>2.5</v>
+      </c>
+      <c r="N3">
+        <v>0.12</v>
+      </c>
+      <c r="O3">
+        <v>1.2</v>
+      </c>
+      <c r="P3">
+        <v>0.4</v>
+      </c>
+      <c r="Q3">
+        <v>0.3</v>
+      </c>
+      <c r="R3">
+        <v>0.15</v>
+      </c>
+      <c r="S3">
+        <v>0.8</v>
+      </c>
+      <c r="T3">
+        <v>0.15</v>
+      </c>
+      <c r="U3">
+        <v>0.05</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>5</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
+      <c r="AA3">
+        <v>0.9</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4447,7 +5369,7 @@
         <v>122</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>123</v>
@@ -4608,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4640,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4672,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="14175" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="493">
   <si>
     <t>unitId</t>
   </si>
@@ -483,31 +483,40 @@
     <t>talent.damage</t>
   </si>
   <si>
+    <t>伤害！</t>
+  </si>
+  <si>
+    <t>提升整体攻击力</t>
+  </si>
+  <si>
+    <t>StatMultiplier</t>
+  </si>
+  <si>
     <t>damage</t>
   </si>
   <si>
-    <t>提升整体攻击力</t>
-  </si>
-  <si>
-    <t>StatMultiplier</t>
-  </si>
-  <si>
     <t>talent.building_hp</t>
   </si>
   <si>
+    <t>城墙！</t>
+  </si>
+  <si>
+    <t>建筑生命值提升</t>
+  </si>
+  <si>
     <t>buildingHp</t>
   </si>
   <si>
-    <t>建筑生命值提升</t>
-  </si>
-  <si>
     <t>talent.gold</t>
   </si>
   <si>
+    <t>财富！</t>
+  </si>
+  <si>
+    <t>提升金币获取速度</t>
+  </si>
+  <si>
     <t>gold</t>
-  </si>
-  <si>
-    <t>提升金币获取速度</t>
   </si>
   <si>
     <t>ruleId</t>
@@ -3347,29 +3356,29 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -3392,10 +3401,10 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C1" t="s">
         <v>102</v>
@@ -3407,110 +3416,110 @@
         <v>103</v>
       </c>
       <c r="F1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G1" t="s">
         <v>104</v>
       </c>
       <c r="H1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I1" t="s">
         <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
         <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3551,19 +3560,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3604,19 +3613,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F5">
         <v>0.3</v>
@@ -3657,19 +3666,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3710,19 +3719,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3775,23 +3784,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3817,27 +3826,27 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -3846,24 +3855,24 @@
         <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -3875,7 +3884,7 @@
         <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3892,53 +3901,53 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -3973,71 +3982,71 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B3">
         <v>300</v>
@@ -4081,65 +4090,65 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B3">
         <v>1.5</v>
@@ -4180,47 +4189,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B3">
         <v>-0.5</v>
@@ -4252,47 +4261,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4324,161 +4333,161 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="P1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="S1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="T1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="U1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="V1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="W1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="X1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Y1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="P2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="R2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="S2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="T2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="U2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="V2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="W2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="X2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Y2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4822,47 +4831,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4894,185 +4903,185 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="H1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="I1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Q1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="S1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="T1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="U1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="V1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="W1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="X1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Z1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AA1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AB1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AC1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="I2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="O2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="P2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Q2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="R2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="S2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="T2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="U2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="V2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="W2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="X2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="Y2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Z2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AA2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AB2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AC2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5219,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5253,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5436,6 +5445,10 @@
   <sheetPr/>
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <cols>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="33.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
@@ -5521,7 +5534,7 @@
         <v>145</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -5535,16 +5548,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -5553,7 +5566,7 @@
         <v>145</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -5567,16 +5580,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -5585,7 +5598,7 @@
         <v>145</v>
       </c>
       <c r="G5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -5611,16 +5624,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5628,16 +5641,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>137</v>
@@ -5645,7 +5658,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
         <v>142</v>
@@ -5662,10 +5675,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>101</v>
@@ -5691,89 +5704,89 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -5791,10 +5804,10 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5826,13 +5839,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D1" t="s">
         <v>93</v>
@@ -5843,16 +5856,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
         <v>137</v>
@@ -5860,10 +5873,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -5877,10 +5890,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
@@ -5894,10 +5907,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
         <v>120</v>
@@ -5911,10 +5924,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
         <v>124</v>
@@ -5928,7 +5941,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
         <v>101</v>
@@ -5957,10 +5970,10 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C1" t="s">
         <v>102</v>
@@ -5969,77 +5982,77 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G1" t="s">
         <v>104</v>
       </c>
       <c r="H1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F3">
         <v>0.7</v>
@@ -6062,19 +6075,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6097,19 +6110,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6132,19 +6145,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6167,19 +6180,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F7">
         <v>0</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="10" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -4900,6 +4900,9 @@
   <sheetPr/>
   <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="10" activeTab="20"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="8" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="491">
   <si>
     <t>unitId</t>
   </si>
@@ -654,13 +654,7 @@
     <t>抽取权重（当前等概率均1）</t>
   </si>
   <si>
-    <t>reward_pool.unit_cactus</t>
-  </si>
-  <si>
     <t>MilitaryUnit</t>
-  </si>
-  <si>
-    <t>reward_pool.unit_ranged_iii</t>
   </si>
   <si>
     <t>reward_pool.tactical_battle_order</t>
@@ -1543,13 +1537,23 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2016,138 +2020,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3359,26 +3369,26 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" t="s">
         <v>247</v>
-      </c>
-      <c r="B2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -3401,10 +3411,10 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C1" t="s">
         <v>102</v>
@@ -3416,110 +3426,110 @@
         <v>103</v>
       </c>
       <c r="F1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G1" t="s">
         <v>104</v>
       </c>
       <c r="H1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I1" t="s">
         <v>61</v>
       </c>
       <c r="J1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L1" t="s">
+        <v>253</v>
+      </c>
+      <c r="M1" t="s">
         <v>254</v>
       </c>
-      <c r="K1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>255</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>256</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>257</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>258</v>
-      </c>
-      <c r="P1" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D2" t="s">
         <v>137</v>
       </c>
       <c r="E2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
         <v>262</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>263</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>264</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>265</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>266</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>267</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>268</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>269</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>270</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>271</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>272</v>
-      </c>
-      <c r="P2" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" t="s">
         <v>275</v>
       </c>
-      <c r="B3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C3" t="s">
-        <v>277</v>
-      </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3560,19 +3570,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3613,19 +3623,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" t="s">
         <v>280</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>281</v>
-      </c>
-      <c r="C5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>283</v>
       </c>
       <c r="F5">
         <v>0.3</v>
@@ -3666,19 +3676,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" t="s">
         <v>284</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>285</v>
-      </c>
-      <c r="C6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>287</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3719,19 +3729,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3787,20 +3797,20 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3826,27 +3836,27 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" t="s">
         <v>294</v>
-      </c>
-      <c r="F1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -3855,24 +3865,24 @@
         <v>137</v>
       </c>
       <c r="E2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2" t="s">
         <v>299</v>
-      </c>
-      <c r="F2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -3884,7 +3894,7 @@
         <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -3904,50 +3914,50 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1" t="s">
         <v>305</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>306</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>307</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>308</v>
-      </c>
-      <c r="F1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" t="s">
         <v>311</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>312</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>313</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>314</v>
-      </c>
-      <c r="F2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -3985,68 +3995,68 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" t="s">
         <v>318</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>319</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>320</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>321</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>322</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>323</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>324</v>
-      </c>
-      <c r="I1" t="s">
-        <v>325</v>
-      </c>
-      <c r="J1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" t="s">
         <v>327</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>328</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>329</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>330</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>331</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>332</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>333</v>
-      </c>
-      <c r="I2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B3">
         <v>300</v>
@@ -4093,62 +4103,62 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" t="s">
         <v>337</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>338</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>339</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>340</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>341</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>342</v>
-      </c>
-      <c r="H1" t="s">
-        <v>343</v>
-      </c>
-      <c r="I1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D2" t="s">
         <v>345</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>346</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>347</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>348</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>349</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>350</v>
-      </c>
-      <c r="H2" t="s">
-        <v>351</v>
-      </c>
-      <c r="I2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B3">
         <v>1.5</v>
@@ -4192,44 +4202,44 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" t="s">
         <v>354</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>355</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>356</v>
-      </c>
-      <c r="E1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" t="s">
         <v>359</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>360</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>361</v>
-      </c>
-      <c r="E2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B3">
         <v>-0.5</v>
@@ -4264,44 +4274,44 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" t="s">
         <v>365</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>366</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>367</v>
-      </c>
-      <c r="E1" t="s">
-        <v>368</v>
-      </c>
-      <c r="F1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D2" t="s">
         <v>370</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>371</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>372</v>
-      </c>
-      <c r="E2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4330,164 +4340,168 @@
   <sheetPr/>
   <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="11" max="11" width="18.625" customWidth="1"/>
+    <col min="12" max="12" width="30.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1" t="s">
         <v>376</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>377</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>378</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>379</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>380</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>381</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>382</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>383</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>384</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>385</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>386</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>387</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>388</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>389</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>390</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>391</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>392</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>393</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>394</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>395</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>396</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>397</v>
-      </c>
-      <c r="X1" t="s">
-        <v>398</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" t="s">
         <v>400</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>401</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>402</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>403</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>404</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>405</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>406</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>407</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>408</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>409</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>410</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>411</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>412</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>413</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>414</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>415</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>416</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>417</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>418</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>419</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>420</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>421</v>
-      </c>
-      <c r="X2" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4520,7 +4534,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -4834,44 +4848,44 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" t="s">
         <v>425</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>426</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>427</v>
-      </c>
-      <c r="E1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D2" t="s">
         <v>430</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>431</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>432</v>
-      </c>
-      <c r="E2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4909,182 +4923,182 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1" t="s">
         <v>436</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>437</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>438</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>439</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>440</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>441</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>442</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>443</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>444</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>445</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>446</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>447</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>448</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>449</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>450</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>451</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>452</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>453</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>454</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>455</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>456</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>457</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>458</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>459</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>460</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>461</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>462</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D2" t="s">
         <v>464</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>465</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>466</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>467</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>468</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>469</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>470</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>471</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>472</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>473</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>474</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>475</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>476</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>477</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>478</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>479</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>480</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>481</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>482</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>483</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>484</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>485</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>486</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>487</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>488</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>489</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>490</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5182,6 +5196,9 @@
   <sheetPr/>
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -5704,6 +5721,12 @@
   <sheetPr/>
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="20.875" customWidth="1"/>
+    <col min="8" max="8" width="27.25" customWidth="1"/>
+    <col min="11" max="11" width="24.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -5839,6 +5862,13 @@
   <sheetPr/>
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="36.625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="26.125" customWidth="1"/>
+    <col min="4" max="4" width="25.375" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -5874,15 +5904,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
         <v>200</v>
       </c>
-      <c r="B3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
+      <c r="C3" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -5891,15 +5921,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>202</v>
+    <row r="4" ht="16.5" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
+        <v>200</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5910,10 +5940,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
         <v>120</v>
@@ -5927,10 +5957,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
         <v>124</v>
@@ -5944,7 +5974,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
         <v>101</v>
@@ -5973,10 +6003,10 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C1" t="s">
         <v>102</v>
@@ -5985,77 +6015,77 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G1" t="s">
         <v>104</v>
       </c>
       <c r="H1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" t="s">
         <v>211</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>212</v>
-      </c>
-      <c r="J1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" t="s">
         <v>216</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>217</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>218</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>219</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>220</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>221</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>222</v>
-      </c>
-      <c r="J2" t="s">
-        <v>223</v>
-      </c>
-      <c r="K2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
         <v>225</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>226</v>
-      </c>
-      <c r="C3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>228</v>
       </c>
       <c r="F3">
         <v>0.7</v>
@@ -6078,19 +6108,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" t="s">
         <v>229</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>230</v>
-      </c>
-      <c r="C4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>232</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6113,19 +6143,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" t="s">
         <v>233</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>234</v>
-      </c>
-      <c r="C5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>236</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6148,19 +6178,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" t="s">
         <v>237</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>238</v>
-      </c>
-      <c r="C6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>240</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6183,19 +6213,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" t="s">
         <v>241</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>242</v>
-      </c>
-      <c r="C7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>244</v>
       </c>
       <c r="F7">
         <v>0</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="8" activeTab="18"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="511">
   <si>
     <t>unitId</t>
   </si>
@@ -1338,6 +1338,36 @@
     <t>talentScreenShakeDuration</t>
   </si>
   <si>
+    <t>cardDragStage1Ratio</t>
+  </si>
+  <si>
+    <t>cardDragStage2Ratio</t>
+  </si>
+  <si>
+    <t>cardDragCardMinScale</t>
+  </si>
+  <si>
+    <t>cardDragCardFadeStart</t>
+  </si>
+  <si>
+    <t>cardDragModelMinScale</t>
+  </si>
+  <si>
+    <t>cardDragModelFadeIn</t>
+  </si>
+  <si>
+    <t>cardDragPreviewRTSize</t>
+  </si>
+  <si>
+    <t>cardDragPreviewWindowSize</t>
+  </si>
+  <si>
+    <t>cardDragPreviewCameraDistance</t>
+  </si>
+  <si>
+    <t>cardDragPreviewPadding</t>
+  </si>
+  <si>
     <t>迷雾纹理刷新间隔（秒）</t>
   </si>
   <si>
@@ -1351,6 +1381,36 @@
   </si>
   <si>
     <t>天赋卡选择震屏时长（秒）</t>
+  </si>
+  <si>
+    <t>拖拽阶段一满程距离 / Canvas参考高度（D1）</t>
+  </si>
+  <si>
+    <t>拖拽阶段二满程距离 / Canvas参考高度（D2，必须大于D1）</t>
+  </si>
+  <si>
+    <t>阶段一末卡牌最小缩放（0~1）</t>
+  </si>
+  <si>
+    <t>卡牌开始淡出的 cardProgress 阈值（0~1）</t>
+  </si>
+  <si>
+    <t>阶段二起始模型预览缩放（0~1）</t>
+  </si>
+  <si>
+    <t>模型淡入占 modelProgress 的比例区间（0~1）</t>
+  </si>
+  <si>
+    <t>模型预览 RenderTexture 边长（像素，正方形）</t>
+  </si>
+  <si>
+    <t>模型预览窗口边长（Canvas 参考单位）</t>
+  </si>
+  <si>
+    <t>预览正交相机与模型的距离（世界单位）</t>
+  </si>
+  <si>
+    <t>预览取景留白系数（正交尺寸 = 模型半径 × 本系数）</t>
   </si>
   <si>
     <t>feel.main</t>
@@ -4840,10 +4900,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>165</v>
       </c>
@@ -4862,30 +4922,90 @@
       <c r="F1" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J1" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1" t="s">
+        <v>432</v>
+      </c>
+      <c r="L1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M1" t="s">
+        <v>434</v>
+      </c>
+      <c r="N1" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" t="s">
+        <v>436</v>
+      </c>
+      <c r="P1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>442</v>
+      </c>
+      <c r="G2" t="s">
+        <v>443</v>
+      </c>
+      <c r="H2" t="s">
+        <v>444</v>
+      </c>
+      <c r="I2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J2" t="s">
+        <v>446</v>
+      </c>
+      <c r="K2" t="s">
+        <v>447</v>
+      </c>
+      <c r="L2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M2" t="s">
+        <v>449</v>
+      </c>
+      <c r="N2" t="s">
+        <v>450</v>
+      </c>
+      <c r="O2" t="s">
+        <v>451</v>
+      </c>
+      <c r="P2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4901,6 +5021,36 @@
       </c>
       <c r="F3">
         <v>0.3</v>
+      </c>
+      <c r="G3">
+        <v>0.2</v>
+      </c>
+      <c r="H3">
+        <v>0.4</v>
+      </c>
+      <c r="I3">
+        <v>0.1</v>
+      </c>
+      <c r="J3">
+        <v>0.6</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>512</v>
+      </c>
+      <c r="N3">
+        <v>512</v>
+      </c>
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -4923,88 +5073,88 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C1" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="D1" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E1" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="F1" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="G1" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="H1" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="I1" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="J1" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K1" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="L1" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="M1" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="N1" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="O1" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="P1" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="Q1" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="R1" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="S1" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="T1" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="U1" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="V1" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="W1" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="X1" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="Y1" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="Z1" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="AA1" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="AB1" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="AC1" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -5012,93 +5162,93 @@
         <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="E2" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="F2" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="G2" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="H2" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="I2" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="J2" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="K2" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="L2" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="M2" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="N2" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="O2" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="P2" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="Q2" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="R2" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="S2" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="T2" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="U2" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="V2" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="W2" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="X2" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="Y2" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="Z2" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="AA2" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="AB2" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="AC2" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5725,6 +5875,7 @@
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="20.875" customWidth="1"/>
     <col min="8" max="8" width="27.25" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
     <col min="11" max="11" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5839,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>50</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="6" activeTab="6"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="8" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="510">
   <si>
     <t>unitId</t>
   </si>
@@ -462,7 +462,7 @@
     <t>卡名（显示用）</t>
   </si>
   <si>
-    <t>描述文案（人工维护，格式化器校验用）</t>
+    <t>描述文案</t>
   </si>
   <si>
     <t>是否启用</t>
@@ -694,9 +694,6 @@
   </si>
   <si>
     <t>#字段说明　稳定ID，如 resource.animals</t>
-  </si>
-  <si>
-    <t>描述文案</t>
   </si>
   <si>
     <t>是否启用（历史保留配置置 false）</t>
@@ -3429,26 +3426,26 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1" t="s">
         <v>243</v>
-      </c>
-      <c r="C1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
         <v>245</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>246</v>
-      </c>
-      <c r="C2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -3471,10 +3468,10 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" t="s">
         <v>249</v>
-      </c>
-      <c r="B1" t="s">
-        <v>250</v>
       </c>
       <c r="C1" t="s">
         <v>102</v>
@@ -3492,104 +3489,104 @@
         <v>104</v>
       </c>
       <c r="H1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I1" t="s">
         <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K1" t="s">
         <v>212</v>
       </c>
       <c r="L1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M1" t="s">
         <v>253</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>254</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>255</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>256</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>257</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
         <v>137</v>
       </c>
       <c r="E2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" t="s">
         <v>260</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>261</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>262</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>263</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>264</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>265</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>266</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>267</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>268</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>269</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>270</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>271</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" t="s">
         <v>273</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>274</v>
       </c>
-      <c r="C3" t="s">
-        <v>275</v>
-      </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3630,19 +3627,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" t="s">
         <v>276</v>
       </c>
-      <c r="B4" t="s">
-        <v>277</v>
-      </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3683,19 +3680,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" t="s">
         <v>278</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>279</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>280</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>281</v>
       </c>
       <c r="F5">
         <v>0.3</v>
@@ -3736,19 +3733,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" t="s">
         <v>282</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>283</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>284</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>285</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3789,19 +3786,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
       <c r="C7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>287</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>288</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3857,20 +3854,20 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3896,27 +3893,27 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" t="s">
         <v>292</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>293</v>
-      </c>
-      <c r="G1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" t="s">
         <v>295</v>
-      </c>
-      <c r="B2" t="s">
-        <v>296</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
@@ -3925,24 +3922,24 @@
         <v>137</v>
       </c>
       <c r="E2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" t="s">
         <v>297</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>298</v>
-      </c>
-      <c r="G2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
         <v>300</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>301</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -3954,7 +3951,7 @@
         <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3974,50 +3971,50 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" t="s">
         <v>303</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>304</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>305</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>306</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>307</v>
-      </c>
-      <c r="G1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" t="s">
         <v>309</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>310</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>311</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>312</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>313</v>
-      </c>
-      <c r="G2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -4055,68 +4052,68 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" t="s">
         <v>316</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>317</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>318</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>319</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>320</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>321</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>322</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>323</v>
-      </c>
-      <c r="J1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" t="s">
         <v>325</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>326</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>327</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>328</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>329</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>330</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>331</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>332</v>
-      </c>
-      <c r="J2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B3">
         <v>300</v>
@@ -4163,62 +4160,62 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" t="s">
         <v>335</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>336</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>337</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>338</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>339</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>340</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>341</v>
-      </c>
-      <c r="I1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
         <v>343</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>344</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>345</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>346</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>347</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>348</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>349</v>
-      </c>
-      <c r="I2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B3">
         <v>1.5</v>
@@ -4262,44 +4259,44 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" t="s">
         <v>352</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>353</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>354</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>355</v>
-      </c>
-      <c r="F1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" t="s">
         <v>357</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>358</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>359</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>360</v>
-      </c>
-      <c r="F2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B3">
         <v>-0.5</v>
@@ -4334,44 +4331,44 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C1" t="s">
         <v>363</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>364</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>365</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>366</v>
-      </c>
-      <c r="F1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2" t="s">
         <v>368</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>369</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>370</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>371</v>
-      </c>
-      <c r="F2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4401,8 +4398,13 @@
   <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="27.75" customWidth="1"/>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="23.125" customWidth="1"/>
     <col min="11" max="11" width="18.625" customWidth="1"/>
     <col min="12" max="12" width="30.75" customWidth="1"/>
+    <col min="22" max="22" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -4410,158 +4412,158 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1" t="s">
         <v>374</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>375</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>376</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>377</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>378</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>379</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>380</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>381</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>382</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>383</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>384</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>385</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>386</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>387</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>388</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>389</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>390</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>391</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>392</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>393</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>394</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>395</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>396</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" t="s">
         <v>398</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>399</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>400</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>401</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>402</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>403</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>404</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>405</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>406</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>407</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>408</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>409</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>410</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>411</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>412</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>413</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>414</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>415</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>416</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>417</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>418</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>419</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>420</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4624,7 +4626,7 @@
         <v>2</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -4908,104 +4910,104 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" t="s">
         <v>423</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>424</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>425</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>426</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>427</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>428</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>429</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>430</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>431</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>432</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>433</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>434</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>435</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>436</v>
-      </c>
-      <c r="P1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2" t="s">
         <v>438</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>439</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>440</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>441</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>442</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>443</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>444</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>445</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>446</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>447</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>448</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>449</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>450</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>451</v>
-      </c>
-      <c r="P2" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -5073,182 +5075,182 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C1" t="s">
         <v>454</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>455</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>456</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>457</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>458</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>459</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>460</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>461</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>462</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>463</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>464</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>465</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>466</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>467</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>468</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>469</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>470</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>471</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>472</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>473</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>474</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>475</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>476</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>477</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>478</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>479</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>480</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2" t="s">
         <v>482</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>483</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>484</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>485</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>486</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>487</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>488</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>489</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>490</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>491</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>492</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>493</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>494</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>495</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>496</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>497</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>498</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>499</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>500</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>501</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>502</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>503</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>504</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>505</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>506</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>507</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>508</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6195,48 +6197,48 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
         <v>214</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>215</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>216</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>217</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>218</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>219</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>220</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>221</v>
-      </c>
-      <c r="K2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
         <v>223</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>224</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>225</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>226</v>
       </c>
       <c r="F3">
         <v>0.7</v>
@@ -6259,19 +6261,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" t="s">
         <v>227</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>228</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>229</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>230</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6294,19 +6296,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" t="s">
         <v>231</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>232</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>233</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>234</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6329,19 +6331,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
         <v>235</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>236</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>237</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>238</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6364,19 +6366,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" t="s">
         <v>239</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>241</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>242</v>
       </c>
       <c r="F7">
         <v>0</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="8" activeTab="18"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="10" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="516">
   <si>
     <t>unitId</t>
   </si>
@@ -225,6 +225,24 @@
     <t>剑客</t>
   </si>
   <si>
+    <t>unit.boss1</t>
+  </si>
+  <si>
+    <t>boss1</t>
+  </si>
+  <si>
+    <t>unit.boss2</t>
+  </si>
+  <si>
+    <t>boss2</t>
+  </si>
+  <si>
+    <t>unit.boss3</t>
+  </si>
+  <si>
+    <t>boss3</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -951,13 +969,13 @@
     <t>子格偏移方向，逗号分隔（如 NE,E,SE，3个方向固定形状）</t>
   </si>
   <si>
-    <t>public.fort</t>
-  </si>
-  <si>
-    <t>堡垒</t>
-  </si>
-  <si>
-    <t>NE,E,SE</t>
+    <t>collectible_01</t>
+  </si>
+  <si>
+    <t>collectible_02</t>
+  </si>
+  <si>
+    <t>collectible_03</t>
   </si>
   <si>
     <t>startingGold</t>
@@ -1594,13 +1612,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11.25"/>
@@ -2077,16 +2101,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2095,119 +2116,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2215,6 +2239,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2750,8 +2777,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -3407,6 +3437,129 @@
       </c>
       <c r="M16">
         <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18">
+        <v>200</v>
+      </c>
+      <c r="G18">
+        <v>12</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1.5</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19">
+        <v>200</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1.5</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>200</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1.5</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3423,29 +3576,29 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -3468,125 +3621,125 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="M1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="N1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="O1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="I2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="J2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="L2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3627,19 +3780,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3680,19 +3833,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F5">
         <v>0.3</v>
@@ -3733,19 +3886,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3786,19 +3939,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3851,23 +4004,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3882,64 +4035,64 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>299</v>
+      <c r="A3" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>58</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -3948,10 +4101,47 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>150</v>
-      </c>
-      <c r="G3" t="s">
-        <v>301</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3968,53 +4158,53 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -4049,71 +4239,71 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="I2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="J2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B3">
         <v>300</v>
@@ -4157,65 +4347,65 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="I1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="F2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="H2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B3">
         <v>1.5</v>
@@ -4256,47 +4446,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B3">
         <v>-0.5</v>
@@ -4328,47 +4518,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4409,161 +4599,161 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="F1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="I1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="J1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="K1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="L1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="N1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="O1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="P1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="Q1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="R1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="S1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="T1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="U1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="V1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="W1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="X1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="Y1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="H2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="I2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="J2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="L2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="N2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Q2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="R2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="S2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="T2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="U2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="V2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="W2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="X2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="Y2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4652,7 +4842,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4661,65 +4851,65 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -4736,16 +4926,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -4762,16 +4952,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4788,16 +4978,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -4814,16 +5004,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4843,16 +5033,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4869,16 +5059,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -4907,107 +5097,107 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="F1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="H1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="I1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="M1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="N1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="O1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="P1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="I2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="K2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="L2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="M2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="N2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="O2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="P2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -5072,185 +5262,185 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="F1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="G1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="H1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="I1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="J1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="K1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="L1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="M1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="N1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="O1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="P1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="Q1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="R1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="S1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="T1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="U1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="V1" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="W1" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="X1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="Y1" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="Z1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="AA1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="AB1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="AC1" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="G2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="H2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="I2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="J2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="K2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="L2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="N2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="O2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="P2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="Q2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="S2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="T2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="U2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="V2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="W2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="X2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="Y2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="Z2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="AA2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AB2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="AC2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5354,36 +5544,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5391,7 +5581,7 @@
         <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -5405,10 +5595,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -5422,10 +5612,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -5442,7 +5632,7 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -5468,7 +5658,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -5477,83 +5667,83 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -5573,22 +5763,22 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G4">
         <v>0.3</v>
@@ -5624,89 +5814,89 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -5720,25 +5910,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -5752,25 +5942,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -5796,16 +5986,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5813,30 +6003,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -5847,13 +6037,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -5883,89 +6073,89 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="M1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="M2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -5983,10 +6173,10 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6025,16 +6215,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6042,29 +6232,29 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D3">
@@ -6075,13 +6265,13 @@
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D4">
@@ -6093,13 +6283,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6110,13 +6300,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6127,13 +6317,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6156,89 +6346,89 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="K2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F3">
         <v>0.7</v>
@@ -6261,19 +6451,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6296,19 +6486,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6331,19 +6521,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6366,19 +6556,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F7">
         <v>0</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="516">
   <si>
     <t>unitId</t>
   </si>
@@ -4037,6 +4037,9 @@
   <sheetPr/>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <cols>
+    <col min="7" max="7" width="50.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -4103,6 +4106,9 @@
       <c r="F3">
         <v>100</v>
       </c>
+      <c r="G3" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
@@ -4123,6 +4129,9 @@
       <c r="F4">
         <v>100</v>
       </c>
+      <c r="G4" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
@@ -4142,6 +4151,9 @@
       </c>
       <c r="F5">
         <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -5227,10 +5227,10 @@
         <v>0.3</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H3">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="I3">
         <v>0.1</v>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="528">
   <si>
     <t>unitId</t>
   </si>
@@ -1600,6 +1600,42 @@
   </si>
   <si>
     <t>mountain.main</t>
+  </si>
+  <si>
+    <t>cardDragPreviewHoverHeight</t>
+  </si>
+  <si>
+    <t>持握悬停高度（世界单位，模型悬停在命中点上方的高度）</t>
+  </si>
+  <si>
+    <t>cardDragPreviewSnapDuration</t>
+  </si>
+  <si>
+    <t>落位补间时长（秒）</t>
+  </si>
+  <si>
+    <t>cardDragPreviewAppearDuration</t>
+  </si>
+  <si>
+    <t>拎起 scale-in 时长（秒，0=不做）</t>
+  </si>
+  <si>
+    <t>cardDragTargetIconHeight</t>
+  </si>
+  <si>
+    <t>落点图标相对地块中心的抬高（世界单位，须高于模型头顶）</t>
+  </si>
+  <si>
+    <t>cardDragTargetIconScale</t>
+  </si>
+  <si>
+    <t>落点图标世界缩放基准</t>
+  </si>
+  <si>
+    <t>cardDragLinkWidth</t>
+  </si>
+  <si>
+    <t>连线宽度（Canvas 参考单位，第二批连线使用）</t>
   </si>
 </sst>
 </file>
@@ -5104,10 +5140,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>171</v>
       </c>
@@ -5156,8 +5192,26 @@
       <c r="P1" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>516</v>
+      </c>
+      <c r="R1" t="s">
+        <v>518</v>
+      </c>
+      <c r="S1" t="s">
+        <v>520</v>
+      </c>
+      <c r="T1" t="s">
+        <v>522</v>
+      </c>
+      <c r="U1" t="s">
+        <v>524</v>
+      </c>
+      <c r="V1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>250</v>
       </c>
@@ -5206,8 +5260,26 @@
       <c r="P2" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" t="s">
+        <v>517</v>
+      </c>
+      <c r="R2" t="s">
+        <v>519</v>
+      </c>
+      <c r="S2" t="s">
+        <v>521</v>
+      </c>
+      <c r="T2" t="s">
+        <v>523</v>
+      </c>
+      <c r="U2" t="s">
+        <v>525</v>
+      </c>
+      <c r="V2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>458</v>
       </c>
@@ -5255,6 +5327,24 @@
       </c>
       <c r="P3">
         <v>1.25</v>
+      </c>
+      <c r="Q3">
+        <v>1.0</v>
+      </c>
+      <c r="R3">
+        <v>0.2</v>
+      </c>
+      <c r="S3">
+        <v>0.08</v>
+      </c>
+      <c r="T3">
+        <v>3.5</v>
+      </c>
+      <c r="U3">
+        <v>1.0</v>
+      </c>
+      <c r="V3">
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/游戏数值配置.xlsx
+++ b/Config/Excel/游戏数值配置.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="10" activeTab="12"/>
+    <workbookView windowWidth="28800" windowHeight="14175" firstSheet="10" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="530">
   <si>
     <t>unitId</t>
   </si>
@@ -96,10 +96,10 @@
     <t>#字段说明　稳定ID，如 unit.archer</t>
   </si>
   <si>
-    <t>迁移期旧整数ID，完成迁移后移除</t>
-  </si>
-  <si>
-    <t>显示名称，不作为关联键</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>显示名称</t>
   </si>
   <si>
     <t>启用状态</t>
@@ -120,13 +120,13 @@
     <t>攻击射程（格）</t>
   </si>
   <si>
-    <t>移动力</t>
+    <t>移动力/速度</t>
   </si>
   <si>
     <t>视野</t>
   </si>
   <si>
-    <t>攻击间隔（秒），非移民必须大于0</t>
+    <t>攻击间隔（秒）</t>
   </si>
   <si>
     <t>卡费</t>
@@ -243,6 +243,15 @@
     <t>boss3</t>
   </si>
   <si>
+    <t>//只调黄色部分就行，其他的是旧版本遗留</t>
+  </si>
+  <si>
+    <t>//伤害公式是：实际伤害 = 攻击力-防御力</t>
+  </si>
+  <si>
+    <t>//若防御力大于攻击力则不造成伤害</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -264,9 +273,6 @@
     <t>迁移期旧整数ID（buildingId）</t>
   </si>
   <si>
-    <t>显示名称</t>
-  </si>
-  <si>
     <t>建筑类型（对应 Enums.BulidingType）</t>
   </si>
   <si>
@@ -1140,13 +1146,13 @@
     <t>meleeAlertRange</t>
   </si>
   <si>
-    <t>河流防御惩罚（负值，如 -0.5）</t>
+    <t>站在河流地块时防御惩罚（负值，如 -0.5）</t>
   </si>
   <si>
     <t>攻击雕像加成（每座，可叠加，如 0.7）</t>
   </si>
   <si>
-    <t>高低地攻击加成（绝对值，攻高+、攻低-，如 0.5）</t>
+    <t>高低地攻击加成：高处打低处+n，低处打高出-n（绝对值，攻高+、攻低-，如 0.5）</t>
   </si>
   <si>
     <t>高地射程加成（格，如 1）</t>
@@ -1323,7 +1329,7 @@
     <t>战术卡可用槽位数量</t>
   </si>
   <si>
-    <t>每次天赋选择展示的候选卡数量</t>
+    <t>每次Hex选择展示的候选卡数量</t>
   </si>
   <si>
     <t>每局公共建筑生成数量上限</t>
@@ -1383,6 +1389,24 @@
     <t>cardDragPreviewPadding</t>
   </si>
   <si>
+    <t>cardDragPreviewHoverHeight</t>
+  </si>
+  <si>
+    <t>cardDragPreviewSnapDuration</t>
+  </si>
+  <si>
+    <t>cardDragPreviewAppearDuration</t>
+  </si>
+  <si>
+    <t>cardDragTargetIconHeight</t>
+  </si>
+  <si>
+    <t>cardDragTargetIconScale</t>
+  </si>
+  <si>
+    <t>cardDragLinkWidth</t>
+  </si>
+  <si>
     <t>迷雾纹理刷新间隔（秒）</t>
   </si>
   <si>
@@ -1428,6 +1452,24 @@
     <t>预览取景留白系数（正交尺寸 = 模型半径 × 本系数）</t>
   </si>
   <si>
+    <t>持握悬停高度（世界单位，模型悬停在命中点上方的高度）</t>
+  </si>
+  <si>
+    <t>落位补间时长（秒）</t>
+  </si>
+  <si>
+    <t>拎起 scale-in 时长（秒，0=不做）</t>
+  </si>
+  <si>
+    <t>落点图标相对地块中心的抬高（世界单位，须高于模型头顶）</t>
+  </si>
+  <si>
+    <t>落点图标世界缩放基准</t>
+  </si>
+  <si>
+    <t>连线宽度（Canvas 参考单位，第二批连线使用）</t>
+  </si>
+  <si>
     <t>feel.main</t>
   </si>
   <si>
@@ -1600,42 +1642,6 @@
   </si>
   <si>
     <t>mountain.main</t>
-  </si>
-  <si>
-    <t>cardDragPreviewHoverHeight</t>
-  </si>
-  <si>
-    <t>持握悬停高度（世界单位，模型悬停在命中点上方的高度）</t>
-  </si>
-  <si>
-    <t>cardDragPreviewSnapDuration</t>
-  </si>
-  <si>
-    <t>落位补间时长（秒）</t>
-  </si>
-  <si>
-    <t>cardDragPreviewAppearDuration</t>
-  </si>
-  <si>
-    <t>拎起 scale-in 时长（秒，0=不做）</t>
-  </si>
-  <si>
-    <t>cardDragTargetIconHeight</t>
-  </si>
-  <si>
-    <t>落点图标相对地块中心的抬高（世界单位，须高于模型头顶）</t>
-  </si>
-  <si>
-    <t>cardDragTargetIconScale</t>
-  </si>
-  <si>
-    <t>落点图标世界缩放基准</t>
-  </si>
-  <si>
-    <t>cardDragLinkWidth</t>
-  </si>
-  <si>
-    <t>连线宽度（Canvas 参考单位，第二批连线使用）</t>
   </si>
 </sst>
 </file>
@@ -1817,12 +1823,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2143,7 +2161,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2167,16 +2185,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2185,90 +2203,93 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2278,6 +2299,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2547,6 +2574,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2813,10 +2845,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="14.625" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="11.625" customWidth="1"/>
+    <col min="12" max="12" width="22.625" customWidth="1"/>
+    <col min="13" max="13" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3394,209 +3434,245 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="s">
+      <c r="A15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="5">
         <v>20</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="5">
         <v>15</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>2</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="5">
         <v>2</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="5">
         <v>0.5</v>
       </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
         <v>1.5</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="5">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" t="s">
+      <c r="A16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="5">
         <v>20</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="5">
         <v>15</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>2</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
         <v>0.5</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
         <v>1.5</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="5">
         <v>40</v>
       </c>
     </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
     <row r="18" spans="1:13">
-      <c r="A18" t="s">
+      <c r="A18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="5">
         <v>200</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="5">
         <v>12</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>2</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5">
         <v>1.5</v>
       </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5">
         <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" t="s">
+      <c r="A19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>15</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="5">
         <v>200</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>12</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>2</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5">
         <v>1.5</v>
       </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
+      <c r="K19" s="5">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5">
         <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="5">
         <v>200</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="5">
         <v>12</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>2</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5">
         <v>1.5</v>
       </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
+      <c r="K20" s="5">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1</v>
+      </c>
+      <c r="M20" s="5">
         <v>300</v>
       </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3612,29 +3688,29 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -3657,125 +3733,125 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3816,19 +3892,19 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C4" t="s">
         <v>282</v>
       </c>
-      <c r="C4" t="s">
-        <v>280</v>
-      </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3869,19 +3945,19 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>0.3</v>
@@ -3922,19 +3998,19 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3975,19 +4051,19 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4040,23 +4116,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4079,53 +4155,53 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>305</v>
+      <c r="A3" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4143,12 +4219,12 @@
         <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>306</v>
+      <c r="A4" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -4166,12 +4242,12 @@
         <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>307</v>
+      <c r="A5" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -4189,7 +4265,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4203,67 +4279,76 @@
   <sheetPr/>
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="37.75" customWidth="1"/>
+    <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="1" t="s">
         <v>311</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="F1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>317</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="F2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B3" s="1">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3">
@@ -4284,74 +4369,80 @@
   <sheetPr/>
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19.875" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B3">
         <v>300</v>
@@ -4392,76 +4483,81 @@
   <sheetPr/>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="24.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>342</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="E1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="E2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="1">
         <v>1.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3">
@@ -4491,61 +4587,69 @@
   <sheetPr/>
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="3" max="3" width="34.25" customWidth="1"/>
+    <col min="4" max="4" width="70.5" customWidth="1"/>
+    <col min="5" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" t="s">
-        <v>357</v>
+        <v>173</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="C1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E1" t="s">
         <v>360</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="F1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" t="s">
-        <v>362</v>
+        <v>252</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="C2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E2" t="s">
         <v>365</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="F2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B3">
+        <v>369</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.5</v>
       </c>
       <c r="C3">
         <v>0.7</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.5</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3">
@@ -4566,47 +4670,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -4640,168 +4744,184 @@
     <col min="2" max="2" width="27.75" customWidth="1"/>
     <col min="3" max="3" width="21.75" customWidth="1"/>
     <col min="4" max="4" width="23.125" customWidth="1"/>
-    <col min="11" max="11" width="18.625" customWidth="1"/>
-    <col min="12" max="12" width="30.75" customWidth="1"/>
-    <col min="22" max="22" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="25.25" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="23.375" customWidth="1"/>
+    <col min="9" max="9" width="29.875" customWidth="1"/>
+    <col min="10" max="10" width="29.25" customWidth="1"/>
+    <col min="11" max="11" width="22.875" customWidth="1"/>
+    <col min="12" max="12" width="11.375" customWidth="1"/>
+    <col min="13" max="13" width="21.125" customWidth="1"/>
+    <col min="14" max="14" width="26.5" customWidth="1"/>
+    <col min="15" max="15" width="18.25" customWidth="1"/>
+    <col min="16" max="16" width="10.75" customWidth="1"/>
+    <col min="17" max="17" width="7.625" customWidth="1"/>
+    <col min="18" max="18" width="19.75" customWidth="1"/>
+    <col min="19" max="19" width="8.75" customWidth="1"/>
+    <col min="20" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="11.625" customWidth="1"/>
+    <col min="22" max="22" width="27.375" customWidth="1"/>
+    <col min="23" max="23" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J1" t="s">
-        <v>387</v>
-      </c>
-      <c r="K1" t="s">
-        <v>388</v>
+        <v>389</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="L1" t="s">
-        <v>389</v>
-      </c>
-      <c r="M1" t="s">
-        <v>390</v>
-      </c>
-      <c r="N1" t="s">
         <v>391</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="1" t="s">
         <v>392</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="P1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q1" t="s">
-        <v>394</v>
-      </c>
-      <c r="R1" t="s">
-        <v>395</v>
+        <v>396</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="S1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="T1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="U1" t="s">
-        <v>398</v>
-      </c>
-      <c r="V1" t="s">
-        <v>399</v>
+        <v>400</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="W1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="X1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Y1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K2" t="s">
-        <v>412</v>
+        <v>413</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="L2" t="s">
-        <v>413</v>
-      </c>
-      <c r="M2" t="s">
-        <v>414</v>
-      </c>
-      <c r="N2" t="s">
         <v>415</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M2" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>418</v>
+      </c>
       <c r="P2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q2" t="s">
-        <v>418</v>
-      </c>
-      <c r="R2" t="s">
-        <v>419</v>
+        <v>420</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="S2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="T2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="U2" t="s">
-        <v>422</v>
-      </c>
-      <c r="V2" t="s">
-        <v>423</v>
+        <v>424</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="W2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="X2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Y2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -4830,19 +4950,19 @@
       <c r="J3">
         <v>20</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>15</v>
       </c>
       <c r="L3">
         <v>13</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>2</v>
       </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
+      <c r="N3" s="1">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1">
         <v>15</v>
       </c>
       <c r="P3">
@@ -4851,7 +4971,7 @@
       <c r="Q3">
         <v>0.3</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>500</v>
       </c>
       <c r="S3">
@@ -4863,7 +4983,7 @@
       <c r="U3">
         <v>2</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>5</v>
       </c>
       <c r="W3">
@@ -4887,10 +5007,13 @@
   <sheetPr/>
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="8" max="8" width="34.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4899,65 +5022,65 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -4974,16 +5097,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -5000,16 +5123,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -5026,16 +5149,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -5051,83 +5174,85 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7">
+      <c r="C7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="1">
         <v>100</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
         <v>120</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8">
+      <c r="A8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="1">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="1">
         <v>100</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
         <v>100</v>
       </c>
-      <c r="I8">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9">
+      <c r="A9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="1">
         <v>100</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
         <v>10</v>
       </c>
-      <c r="I9">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1">
         <v>1.5</v>
       </c>
     </row>
@@ -5145,143 +5270,143 @@
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q1" t="s">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="R1" t="s">
-        <v>518</v>
+        <v>446</v>
       </c>
       <c r="S1" t="s">
-        <v>520</v>
+        <v>447</v>
       </c>
       <c r="T1" t="s">
-        <v>522</v>
+        <v>448</v>
       </c>
       <c r="U1" t="s">
-        <v>524</v>
+        <v>449</v>
       </c>
       <c r="V1" t="s">
-        <v>526</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="G2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="H2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="I2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="J2" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="K2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="L2" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="M2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="N2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="O2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="P2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="Q2" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="R2" t="s">
-        <v>519</v>
+        <v>467</v>
       </c>
       <c r="S2" t="s">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="T2" t="s">
-        <v>523</v>
+        <v>469</v>
       </c>
       <c r="U2" t="s">
-        <v>525</v>
+        <v>470</v>
       </c>
       <c r="V2" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="B3">
         <v>0.05</v>
@@ -5329,7 +5454,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>0.2</v>
@@ -5341,10 +5466,10 @@
         <v>3.5</v>
       </c>
       <c r="U3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5364,185 +5489,185 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="C1" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="D1" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="E1" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="F1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="G1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="H1" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="I1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="J1" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="K1" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="L1" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="M1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="N1" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="O1" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="P1" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="Q1" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="R1" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="S1" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="T1" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="U1" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="V1" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="W1" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="X1" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="Y1" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="Z1" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="AA1" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="AB1" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="AC1" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="C2" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="D2" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="E2" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="F2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="G2" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="H2" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="I2" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="J2" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="K2" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="L2" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="M2" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="N2" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="O2" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="P2" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="Q2" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="R2" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="S2" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="T2" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="U2" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="V2" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="W2" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="X2" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="Y2" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="Z2" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="AA2" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AB2" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="AC2" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5641,108 +5766,112 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
+    <col min="2" max="2" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>100</v>
+      <c r="E1" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
+      <c r="A4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
+      <c r="A5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
+      <c r="B6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5755,148 +5884,155 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="F1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B2" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C2" t="s">
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="J2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="K2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D3" t="s">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="D3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <v>1.3</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>1.3</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>5</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G4">
+      <c r="D4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="1">
         <v>0.3</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5912,93 +6048,95 @@
   <cols>
     <col min="3" max="3" width="16.25" customWidth="1"/>
     <col min="4" max="4" width="33.375" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" t="s">
-        <v>108</v>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" t="s">
         <v>142</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" t="s">
-        <v>150</v>
+      <c r="C3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -6012,25 +6150,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>153</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>151</v>
-      </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -6044,25 +6182,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" t="s">
-        <v>159</v>
+      <c r="C5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -6088,16 +6226,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6105,30 +6243,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -6139,13 +6277,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -6166,133 +6304,140 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="20.875" customWidth="1"/>
-    <col min="8" max="8" width="27.25" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="14.75" customWidth="1"/>
+    <col min="7" max="7" width="32.75" customWidth="1"/>
+    <col min="8" max="8" width="37.5" customWidth="1"/>
+    <col min="9" max="9" width="18.375" customWidth="1"/>
     <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="24.625" customWidth="1"/>
+    <col min="11" max="11" width="16.5" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H1" t="s">
+      <c r="F1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K1" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="1">
         <v>20</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>20</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>20</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>20</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="G3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>10</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>50</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>50</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>50</v>
       </c>
     </row>
@@ -6317,16 +6462,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -6334,29 +6479,29 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D3">
@@ -6367,13 +6512,13 @@
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D4">
@@ -6385,13 +6530,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6402,13 +6547,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6419,13 +6564,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6448,89 +6593,89 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>0.7</v>
@@ -6553,19 +6698,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6588,19 +6733,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6623,19 +6768,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6658,19 +6803,19 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F7">
         <v>0</v>
